--- a/output/applied_sciences/daad-programs.xlsx
+++ b/output/applied_sciences/daad-programs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="725">
   <si>
     <t>ID</t>
   </si>
@@ -2201,6 +2201,24 @@
     <t>https://www.daad.de/en/studying-in-germany/universities/all-degree-programmes/detail/university-of-applied-sciences-neu-ulm-artificial-intelligence-and-health-informatics-w77135/?hec-id=w77135</t>
   </si>
   <si>
+    <t>w77852</t>
+  </si>
+  <si>
+    <t>Fachhochschule of Erfurt</t>
+  </si>
+  <si>
+    <t>Einmalige Kosten für thoska+: 20,00 Euro https://www.fh-erfurt.de/studienorganisation/gebuehren-und-beitraege/</t>
+  </si>
+  <si>
+    <t>Zum Studium berechtigen u. a.: - ein erster Hochschulabschluss oder Abschluss einer staatlichen oder staatlich anerkannten Berufsakademie auf dem Gebiet des Software Engineering mit mindestens 210 Kreditpunkten - Sprachkenntnise in englischer Sprache auf dem Niveau B2 - Haben Bewerber in einem oben genannten Studiengänge nur 180 Kreditpunkte erworben, können die fehlenden 30 Kreditpunkte aus dem Bachelorstudiengang studienbegleitend erworben werden.</t>
+  </si>
+  <si>
+    <t>https://www.daad.de/en/studying-in-germany/universities/all-degree-programmes/detail/fachhochschule-of-erfurt-software-engineering-w77852/?hec-id=w77852</t>
+  </si>
+  <si>
+    <t>https://www.fh-erfurt.de/fakultaeten-und-fachrichtungen/gebaeudetechnik-und-informatik/angewandte-informatik/master-software-engineering</t>
+  </si>
+  <si>
     <t>w7790</t>
   </si>
   <si>
@@ -2226,6 +2244,18 @@
   </si>
   <si>
     <t>https://www.hof-university.com/graduate-school/masters-program-full-time/software-engineering-for-industrial-applications-meng.html</t>
+  </si>
+  <si>
+    <t>w78022</t>
+  </si>
+  <si>
+    <t>Business Informatics</t>
+  </si>
+  <si>
+    <t>https://www.daad.de/en/studying-in-germany/universities/all-degree-programmes/detail/university-of-applied-sciences-emdenleer-business-informatics-w78022/?hec-id=w78022</t>
+  </si>
+  <si>
+    <t>https://www.hs-emden-leer.de/business-informatics</t>
   </si>
   <si>
     <t>w9362</t>
@@ -2633,7 +2663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O105"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -7398,66 +7428,66 @@
         <v>699</v>
       </c>
       <c r="B102" t="s">
-        <v>266</v>
+        <v>700</v>
       </c>
       <c r="C102" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="D102" t="s">
-        <v>129</v>
+        <v>224</v>
       </c>
       <c r="E102" t="s">
-        <v>700</v>
+        <v>34</v>
       </c>
       <c r="F102" t="s">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="G102" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H102" t="s">
         <v>22</v>
       </c>
       <c r="I102" t="s">
+        <v>24</v>
+      </c>
+      <c r="J102" t="s">
         <v>701</v>
       </c>
-      <c r="J102" t="s">
+      <c r="K102" t="s">
+        <v>25</v>
+      </c>
+      <c r="L102" t="s">
+        <v>217</v>
+      </c>
+      <c r="M102" t="s">
         <v>702</v>
       </c>
-      <c r="K102" t="s">
-        <v>25</v>
-      </c>
-      <c r="L102" t="s">
+      <c r="N102" t="s">
         <v>703</v>
       </c>
-      <c r="M102" t="s">
+      <c r="O102" t="s">
         <v>704</v>
-      </c>
-      <c r="N102" t="s">
-        <v>705</v>
-      </c>
-      <c r="O102" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B103" t="s">
-        <v>708</v>
+        <v>266</v>
       </c>
       <c r="C103" t="s">
-        <v>709</v>
+        <v>267</v>
       </c>
       <c r="D103" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E103" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="F103" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G103" t="s">
         <v>48</v>
@@ -7466,25 +7496,119 @@
         <v>22</v>
       </c>
       <c r="I103" t="s">
-        <v>24</v>
+        <v>707</v>
       </c>
       <c r="J103" t="s">
-        <v>24</v>
+        <v>708</v>
       </c>
       <c r="K103" t="s">
         <v>25</v>
       </c>
       <c r="L103" t="s">
+        <v>709</v>
+      </c>
+      <c r="M103" t="s">
+        <v>710</v>
+      </c>
+      <c r="N103" t="s">
         <v>711</v>
       </c>
-      <c r="M103" t="s">
+      <c r="O103" t="s">
         <v>712</v>
       </c>
-      <c r="N103" t="s">
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>713</v>
       </c>
-      <c r="O103" t="s">
+      <c r="B104" t="s">
+        <v>54</v>
+      </c>
+      <c r="C104" t="s">
+        <v>55</v>
+      </c>
+      <c r="D104" t="s">
+        <v>56</v>
+      </c>
+      <c r="E104" t="s">
         <v>714</v>
+      </c>
+      <c r="F104" t="s">
+        <v>603</v>
+      </c>
+      <c r="G104" t="s">
+        <v>21</v>
+      </c>
+      <c r="H104" t="s">
+        <v>81</v>
+      </c>
+      <c r="I104" t="s">
+        <v>365</v>
+      </c>
+      <c r="J104" t="s">
+        <v>24</v>
+      </c>
+      <c r="K104" t="s">
+        <v>25</v>
+      </c>
+      <c r="L104" t="s">
+        <v>84</v>
+      </c>
+      <c r="M104" t="s">
+        <v>24</v>
+      </c>
+      <c r="N104" t="s">
+        <v>715</v>
+      </c>
+      <c r="O104" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>717</v>
+      </c>
+      <c r="B105" t="s">
+        <v>718</v>
+      </c>
+      <c r="C105" t="s">
+        <v>719</v>
+      </c>
+      <c r="D105" t="s">
+        <v>138</v>
+      </c>
+      <c r="E105" t="s">
+        <v>720</v>
+      </c>
+      <c r="F105" t="s">
+        <v>35</v>
+      </c>
+      <c r="G105" t="s">
+        <v>48</v>
+      </c>
+      <c r="H105" t="s">
+        <v>22</v>
+      </c>
+      <c r="I105" t="s">
+        <v>24</v>
+      </c>
+      <c r="J105" t="s">
+        <v>24</v>
+      </c>
+      <c r="K105" t="s">
+        <v>25</v>
+      </c>
+      <c r="L105" t="s">
+        <v>721</v>
+      </c>
+      <c r="M105" t="s">
+        <v>722</v>
+      </c>
+      <c r="N105" t="s">
+        <v>723</v>
+      </c>
+      <c r="O105" t="s">
+        <v>724</v>
       </c>
     </row>
   </sheetData>
